--- a/bot_evaluation_with_comments.xlsx
+++ b/bot_evaluation_with_comments.xlsx
@@ -1,47 +1,232 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CTC_HEALTH\Projects\Evaluation_Cycle\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DED5213-67F1-4672-85B9-1596D753FD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Evaluation Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Evaluation Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={D642B5E2-1544-470C-9EA1-65C26A174C5F}</author>
+    <author>tc={C05F9480-1E11-418D-AD2B-A559881FA535}</author>
+  </authors>
+  <commentList>
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{D642B5E2-1544-470C-9EA1-65C26A174C5F}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This question does not really differentiate responses tbh. </t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="1" shapeId="0" xr:uid="{C05F9480-1E11-418D-AD2B-A559881FA535}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This question shows how the replies shorten when given a strict time limit. Good for testing but I don't think this would ever be said in our context. </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>The Traditionalist</t>
+  </si>
+  <si>
+    <t>The Traditionalist Eval</t>
+  </si>
+  <si>
+    <t>The Traditionalist Comment</t>
+  </si>
+  <si>
+    <t>The Traditionalist Eval_Aboubakr</t>
+  </si>
+  <si>
+    <t>The Traditionalist Comment_Aboubakr</t>
+  </si>
+  <si>
+    <t>The Traditionalist Eval_Thomas</t>
+  </si>
+  <si>
+    <t>The Traditionalist Comment_Thomas</t>
+  </si>
+  <si>
+    <t>The Innovator</t>
+  </si>
+  <si>
+    <t>The Innovator Eval</t>
+  </si>
+  <si>
+    <t>The Innovator Comment</t>
+  </si>
+  <si>
+    <t>The Innovator Eval_Aboubakr</t>
+  </si>
+  <si>
+    <t>The Innovator Comment_Aboubakr</t>
+  </si>
+  <si>
+    <t>The Innovator Eval_Thomas</t>
+  </si>
+  <si>
+    <t>The Innovator Comment_Thomas</t>
+  </si>
+  <si>
+    <t>The Evidence Purist</t>
+  </si>
+  <si>
+    <t>The Evidence Purist Eval</t>
+  </si>
+  <si>
+    <t>The Evidence Purist Comment</t>
+  </si>
+  <si>
+    <t>The Evidence Purist Eval_Aboubakr</t>
+  </si>
+  <si>
+    <t>The Evidence Purist Comment_Aboubakr</t>
+  </si>
+  <si>
+    <t>The Evidence Purist Eval_Thomas</t>
+  </si>
+  <si>
+    <t>The Evidence Purist Comment_Thomas</t>
+  </si>
+  <si>
+    <t>Hey, doctor. Um, help me understand. How do you make treatment decisions?</t>
+  </si>
+  <si>
+    <t>A new therapy is just approved. What makes you start using it in practice?</t>
+  </si>
+  <si>
+    <t>What kind of evidence convinces you most—real-world data, RCTs, meta-analyses, expert opinion?</t>
+  </si>
+  <si>
+    <t>If guidelines don’t mention a new option yet, how do you act?</t>
+  </si>
+  <si>
+    <t>How do you interpret surrogate endpoints vs ‘hard’ clinical outcomes?</t>
+  </si>
+  <si>
+    <t>What’s your approach when evidence is promising but long-term safety is unknown?</t>
+  </si>
+  <si>
+    <t>Describe how you evaluate a pivotal study in 60 seconds.</t>
+  </si>
+  <si>
+    <t>If two trials conflict, what do you do?</t>
+  </si>
+  <si>
+    <t>When do you trust real-world evidence?</t>
+  </si>
+  <si>
+    <t>How do you decide between a familiar standard vs a new option with modest benefit?</t>
+  </si>
+  <si>
+    <t>What role do KOLs and conferences play in your decisions?</t>
+  </si>
+  <si>
+    <t>Tell me about a time you changed your practice—what triggered it?</t>
+  </si>
+  <si>
+    <t>How do you handle off-label ideas suggested by colleagues?</t>
+  </si>
+  <si>
+    <t>What makes you reject a therapy even if it’s popular?</t>
+  </si>
+  <si>
+    <t>If a rep/MSL has new data, what do you ask first?</t>
+  </si>
+  <si>
+    <t>What is your default: ‘try early in a few patients’ vs ‘wait until standard of care’—and why?</t>
+  </si>
+  <si>
+    <t>For a meaningful benefit, what level of risk or uncertainty are you willing to accept—and how does that change by patient type?</t>
+  </si>
+  <si>
+    <t>If a new option reduces events by an absolute 1% but adds a 0.3% serious adverse event risk, how do you think about that tradeoff?</t>
+  </si>
+  <si>
+    <t>If a therapy requires extra lab monitoring or follow-ups, when is that still worth it—and when is it a deal-breaker?</t>
+  </si>
+  <si>
+    <t>If the trial population doesn’t resemble your real patients (older, comorbid, polypharmacy), how do you translate the results to your practice?</t>
+  </si>
+  <si>
+    <t>If you start a new therapy and results are “okay but not great,” what makes you stop it or revert back?</t>
+  </si>
+  <si>
+    <t>When a new drug enters an established class, do you assume it’s a class effect—or do you treat it as different until proven?</t>
+  </si>
+  <si>
+    <t>In your setting, who influences whether a therapy actually gets used—pharmacy, committee, admin, patients—and how do you navigate that?</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -63,88 +248,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Aboubakr Saleh" id="{1478022F-B186-44D7-8DC3-9041B8FC86DA}" userId="S::aboubakr.saleh@ctchealth.ch::50cbb8b8-e14e-4131-bbc3-c4f7bddca2c3" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,126 +564,239 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A4" dT="2026-01-02T12:30:40.37" personId="{1478022F-B186-44D7-8DC3-9041B8FC86DA}" id="{D642B5E2-1544-470C-9EA1-65C26A174C5F}">
+    <text xml:space="preserve">This question does not really differentiate responses tbh. </text>
+  </threadedComment>
+  <threadedComment ref="A8" dT="2026-01-02T11:37:15.81" personId="{1478022F-B186-44D7-8DC3-9041B8FC86DA}" id="{C05F9480-1E11-418D-AD2B-A559881FA535}">
+    <text xml:space="preserve">This question shows how the replies shorten when given a strict time limit. Good for testing but I don't think this would ever be said in our context. </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:V27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="2"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="40" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="40" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="40" customWidth="1"/>
+    <col min="16" max="16" width="50" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="40" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="40" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>The Traditionalist</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>The Traditionalist Eval</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>The Traditionalist Comment</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>The Innovator</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>The Innovator Eval</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>The Innovator Comment</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>The Evidence Purist</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>The Evidence Purist Eval</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>The Evidence Purist Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Hey, doctor. Um, help me understand. How do you make treatment decisions?</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Well, all right, I mean—look, when it comes to treatment decisions, I always start with the established guidelines. That’s, let’s say, my baseline. I don’t reinvent the wheel with every patient. The M...</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+    <row r="1" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Let me think for a moment… So, the way I approach treatment decisions, it’s—well, it’s layered. First and foremost, I look at the patient’s clinical need and, you know, exactly where we are in the dis...</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>The assistant's response touches on treatment decisions but lacks specific references to the Innovator persona's core motivations, such as intrinsic motivation for innovation and data-driven decision-making. To improve, the response should include elements like excitement for new therapies and reliance on robust clinical data, aligning more closely with the Innovator's mindset.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>One second… … … let me take this call… … … Yes, this is Dr. Lindner… … … … … alright… … … … … yeah, okay… … … … … No, transfuse only if hemoglobin drops below seven… … … … check levels again in six ho...</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>The assistant's response does not address the user's question about treatment decisions and instead focuses on a phone call regarding a specific case. It lacks any evidence-based reasoning or principles that align with the Evidence Purist persona. To improve, the assistant should provide a clear explanation of how treatment decisions are made based on scientific evidence and guidelines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="n"/>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>